--- a/data/file_generation/input/data_79/辞工汇总表2025年度.xlsx
+++ b/data/file_generation/input/data_79/辞工汇总表2025年度.xlsx
@@ -4149,26 +4149,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14E2D2FE-F502-4B2D-8995-23D16BB5F5B4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{461757D4-1B53-4410-88E4-EDDC9D27C60A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7F86525-6911-486A-8EDB-35EA24E24DA2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67061C6A-DA97-4627-9006-4C90C0055F95}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE36FA95-E1B7-4BD5-BE7B-00197E0C41D5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD6C8140-1A0D-4F32-855B-AB01FB73B4E5}"/>
 </file>